--- a/table/Datas/#StatusEffect.xlsx
+++ b/table/Datas/#StatusEffect.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,20 +536,11 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -609,7 +600,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
         <v>1</v>
       </c>
@@ -650,6 +640,51 @@
         </is>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>이동속도 -30% 감소</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PercentAdd</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
     </row>
